--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -126,144 +126,144 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
+          <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Baucco</t>
+          <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shawn McWilliams</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Fletcher Stevens</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Miers</t>
+          <t xml:space="preserve">JAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Don Andrews</t>
+          <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bud Deflorio</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Palmeri</t>
+          <t xml:space="preserve">Denny Miers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Salerno</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Myers</t>
+          <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pat Bruckman</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">Justin Myers</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
+          <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
     </row>
@@ -275,19 +275,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">Ross Locigno</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ross Locigno</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVfbbttGEP2V7aCP63h5kZDypbBipIEQFUYUwEBJPqzJtbQQtesuVxZUw/9ezJAWL0pi1WhehDU5czhz5swh/QT+8KAggcLZur4onFKbi1o+KuDgbO2Vg+QJriCBv9RGsWt1X1mnbWbmdm3YTO6KwmZmuZZ7wxbFra4qLbd1Zr4cpGG3SpXtcaGVqzNzrYw5vPwxt4p9toVeGQscZpDAtd2t2EwZo7zPzEJvFJs5tdL+H+Uyc1VJw5aFxXvX1rArUzq1rzPz0UmzYcvNrqoOmZntyl6dH9ZO1+xGVlvlNHD4gI+Rj4rd2H1ThaytYUtZKWdsZv6UXrGlV4/K1JmZOeXZVycPlXWZme9qrw1bHChx5mSJeTIzN9KzmdsVm600wOEaEvhYKV+sleuw5ur+vsllc/euZbDtPzNzvWUzZ/cmM38o61aKfZJrk5n51SIzX2xdH6l65oCIvoYkhWWlHy1bFk5u7yoc2vRyejntX7hda6/YV6W6izmHB6fuEeAJJCTQjQg43EECY9b2kATimX8nus/Zq8Hzq8U4pqeKMxBPo/uyeT16PJlxRlMgldqb90nU8N7dS6uo+Vc56Av21eAfdXeK/EpzJwkDab06ux8QchJ83I//v+jhKh3Dcw5I7K3Sq7WHRHDwe7uQBi3MyC3a3Ne9vViQjRwXZOXs7gF3IU2HJgccBuYAOU9hbHXoXD3DgTznaTqseLhMCDIa6Un/DcjQHwcegyBDe8RiXyykX0Srx8GYMXs0ym5YTe5IoT1Lahs42i8ldy7Z5g/XbrDO9PTu7YGFXy3atM7i8fJwyvTczrkxoOegkOf5Mwe/U3UpD72Jf5JmZR+VY19UObRBDqWqC0jgRhcb5pXc1kwb5teK3UnHFtaU8sAMiukX9lnJUpsV21qjDmyvjcG6gov37IGy10o7wmDe4u2XK84+rA/sgtXKPSjjtVHMulK5d+9Qt7WXzkMC4rckEujsztqtVjXWj0eS5akqe+x9R5Pd7DFgIMf+aJpZ9GU2kOY3Zdab0akUBrrB24Pl+OYuDEd6snCjV8FQaz8UMk9h9GI+XTQEGJvJUFYYcVys001o3hbD9UIh1spo6+gdPSb4u3zxMVuDZvm4m0GdvK1kWB+sUOrarFBQfou/couCCwTJH4838kCatx6ZIQmX2qnCVwf61hBdVthlBbVnF+zXQAjOQlPi+b3gLHJ0nArOYr/GYywyc6NNfbncaFPjlfC9uPydoIOfBx3+NGi/+0nQzxzWulS32hhtVjUk3u0UB68UPrBWf6OY/BZoJsQe9Ylfc8rRbHFWacQDHvIJF3zK47xhmS7ihZDHfJI3/KQRXZjwmAse5JwEkgoec7wx4SEPUMmtnSK2aNCCJj9oMsTz0ceeQCATQRJPgEPQGJsgY7MPXm/1P6p8aatSsmwzBMVGz83ru1WroK/Tlabba1uVkEQc9lJ7SKYcClt7SCIhpk375JTD2vmIihy/JxAwOBsQSYtbwCjnaUw0IuSURx1geDZgyAURjlVihVhf1D5CdIDR2YARtRcSBAKGPCBwnOmkA4zPBoypOcGjlsOATo1Iph3g5GxA5E60TXYVNjT0AKdnA07baoYVUn3Uck5yeoN4mlFMjnU2NQbDWf838UTdzqXHM63bm8SDyVQPF60akQxs/43iGbjCyBDeJJ5m1lRlyyFWiTW+UTzHSRPgi9QRMHibeHr6y3k6bauNWw5ztGH6FqT/CBp2olZlAaWE1FDDF0ompFG0JppOGv4IGrOn9GUr6IGi3fiYEEPas5Bw4sas07jZNsKhRSYcPActDkZMCCdo9R+SygTh4NMbo5rSeiGOwEjCoXHkec6hssUGvThN72VVK37Gb85/Umz+/C8=</t>
+          <t xml:space="preserve">CC1:tVdNb+M2EP0rLNEjs6Ek29jqUsQbbBfGugjiBQJU0oGRJjZhmUwpOoY3yH8vZqRYH27XbtpcDIbiPM68efOkPHO/fwQe89zZqrrIHcD6olJPwAV3tvLgePzMr3jM/4A1sGt4KK3TNjUzuzJsqrZ5blOzWKmdYfP8TpelVpsqNbd7ZdgdQNEs5xpclZprMGb/+sfMAvtqc700lgs+5TG/ttslm4Ix4H1q5noNbOpgqf13cKm5KpVhi9zis2tr2JUpHOyq1Hx2yqzZYr0ty31qptuik+enldMVu1HlBpzmgn/Ca9QTsBu7q7NQlTVsoUpwxqbmd+WBLTw8galSM3Xg2Ten9qV1qZltK68Nm+8pcOpUgXEqNTfKs6nb5uuNMlzwax7zzyX4fAWuxZrBw0Mdy2buQ8NgU39qZnrDps7uTGp+A+uWwL6olUnN7GqemltbVQeqXgRHRF/xOOGLUj9Ztsid2tyX2LTJ5eRy0t24W2kP7BtAu5kJ/ujgAQGeueIxb1vEBb/nMR+ytuNxIF/EP5zucnby8OxqPjzTUcUZiMenu7I5fXrYmWFEnSCl2un30an+s/vXUlHzJznoCvbk4R9Vd4x8orijgJ60TvbuB4QcHT7Mx/+fdH+UDsczwZHYO9DLleexFNzv7FwZtDCjNmhz33b2Yk42chiQpbPbR5yFJOmbHBe8Zw48EwkfWh06V8dweJaJJOln3B8mBBm09Kj+GqTvjz2PQZC+PWKyrxbSTaLRY6/NGD1oZdusOnag0I4lNQUc7JeCW5ds4vtj1xtnur19e2DiV/MmrLV43O53me5tnRsPdByUZ1n2IrjfQlWofafjX5RZ2idw7BaKvg0KXkCV85jf6HzNPKhNxbRhfgXsXjk2t6ZQe2ZQTD+xr6AKbZZsYw3s2U4bg3kFFx/ZI0WvQDvCYN7i49cdZx9Xe3bBKnCPYLw2wKwrwH34gLqtvHKex1z+EkcSnd1Zu9FQYf64JFn+ZzUh4WRqXfr+VkJH6qbY3hCIwZAct7M/DyIZunlXG/j4hNZOjMGPpCj6Q9DTPD7sya0zAnjrYZiGOkPQvmkOhYpCrMBo6+gd3S+gn++g9h51g2oGtQ/SEk2L++zxJUpdmyUKym/wV21QcIEk+ePyRu1J89ajaEjChXaQ+3JP3xqyjQrbqKDy7IL9HEgpWGgKXH+UgkWOlhMp2MivcDmSqbnRprpcrLWpcCf8KC9/Jejg/aDDd4P223eCfhF8pQu408Zos6x47N0WBPcAeGEFf6KY/IZTT4g9qhO/5sBRb7FXSSQCEYqxkGIiRlnNMm3iRihGYpzV/CQRbYzFSEgRZIIEkkgxEvhgLEIRoJIbO0VsWaMFdXxQR8iXg489c4lMBPFozAUPamOTZGz20euN/g7Fa1klqKKJkHQ2eqlf341aJX2dLjU9Xtmy4HEk+E5pz+OJ4LmtPI8jKSd1+eSU/dzFgIoMvycQMDgbEEkbNYBRJpIR0YiQExG1gOHZgKGQRDhmiRliflFzhWwBo7MBIyovJAgEDEVA4NjTcQs4OhtwRMVJETUcBrSqRTJpAcdnAyJ3simyzbCmoQM4ORtw0mTTz5Dyo5IzktMbxFO3YnzIs84x6Pf634knamcuOaxp3N4kHgymfIRs1IhkYPlvFE/PFQaG8Cbx1L2mLBsOMUvM8Y3iOXSaAF+ljoDB28TT0V8mkkmT7ajhMEMbpm9B+o+gZidqVBZQSEgF1XyhZEJqRWOiybjmj6AxekJftpIulM3EjwgxpDkLCWdUm3UyqqeNcGiQCQfXQYODJ8aEEzT6D0llknDw9tqoJjReiCPxJOFQO7IsE7y0+Rq9OEkeVFmBOOM3E+90Nnv5Cw==</t>
         </is>
       </c>
     </row>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -697,29 +697,29 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="7">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="7">
+      <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="7">
+      <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="7">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="7">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -763,7 +763,7 @@
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="7">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -785,19 +785,19 @@
           <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="7">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="7">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="7">
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1051,17 +1051,17 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="7">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr" s="7">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="7">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1122,12 +1122,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr" s="7">
+      <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr" s="7">
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1159,7 +1159,7 @@
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="7">
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1171,7 +1171,7 @@
           <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr" s="7">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
@@ -1181,7 +1181,7 @@
           <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="7">
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr" s="7">
+      <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -1233,7 +1233,7 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr" s="7">
+      <c r="B34" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr" s="7">
+      <c r="A35" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
@@ -1270,7 +1270,7 @@
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="7">
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1287,12 +1287,12 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="7">
+      <c r="B36" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="7">
+      <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1319,7 +1319,7 @@
           <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="7">
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1353,17 +1353,17 @@
           <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="7">
+      <c r="B39" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="7">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="7">
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -126,144 +126,144 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Miers</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Palmeri</t>
+          <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Denny Miers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shawn McWilliams</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Salerno</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
+          <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Baucco</t>
+          <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bud Deflorio</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pat Bruckman</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Don Andrews</t>
+          <t xml:space="preserve">Justin Myers</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Myers</t>
+          <t xml:space="preserve">Fletcher Stevens</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
@@ -275,19 +275,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">JAM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ross Locigno</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
     </row>
@@ -697,29 +697,29 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -758,12 +758,12 @@
           <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -785,19 +785,19 @@
           <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1006,7 +1006,7 @@
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
@@ -1051,17 +1051,17 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1122,12 +1122,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1154,12 +1154,12 @@
           <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1171,7 +1171,7 @@
           <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
@@ -1181,7 +1181,7 @@
           <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -1233,7 +1233,7 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
@@ -1265,12 +1265,12 @@
           <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1287,12 +1287,12 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1319,7 +1319,7 @@
           <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1353,17 +1353,17 @@
           <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
@@ -2113,7 +2113,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVdNb+M2EP0rLNEjs6Ek29jqUsQbbBfGugjiBQJU0oGRJjZhmUwpOoY3yH8vZqRYH27XbtpcDIbiPM68efOkPHO/fwQe89zZqrrIHcD6olJPwAV3tvLgePzMr3jM/4A1sGt4KK3TNjUzuzJsqrZ5blOzWKmdYfP8TpelVpsqNbd7ZdgdQNEs5xpclZprMGb/+sfMAvtqc700lgs+5TG/ttslm4Ix4H1q5noNbOpgqf13cKm5KpVhi9zis2tr2JUpHOyq1Hx2yqzZYr0ty31qptuik+enldMVu1HlBpzmgn/Ca9QTsBu7q7NQlTVsoUpwxqbmd+WBLTw8galSM3Xg2Ten9qV1qZltK68Nm+8pcOpUgXEqNTfKs6nb5uuNMlzwax7zzyX4fAWuxZrBw0Mdy2buQ8NgU39qZnrDps7uTGp+A+uWwL6olUnN7GqemltbVQeqXgRHRF/xOOGLUj9Ztsid2tyX2LTJ5eRy0t24W2kP7BtAu5kJ/ujgAQGeueIxb1vEBb/nMR+ytuNxIF/EP5zucnby8OxqPjzTUcUZiMenu7I5fXrYmWFEnSCl2un30an+s/vXUlHzJznoCvbk4R9Vd4x8orijgJ60TvbuB4QcHT7Mx/+fdH+UDsczwZHYO9DLleexFNzv7FwZtDCjNmhz33b2Yk42chiQpbPbR5yFJOmbHBe8Zw48EwkfWh06V8dweJaJJOln3B8mBBm09Kj+GqTvjz2PQZC+PWKyrxbSTaLRY6/NGD1oZdusOnag0I4lNQUc7JeCW5ds4vtj1xtnur19e2DiV/MmrLV43O53me5tnRsPdByUZ1n2IrjfQlWofafjX5RZ2idw7BaKvg0KXkCV85jf6HzNPKhNxbRhfgXsXjk2t6ZQe2ZQTD+xr6AKbZZsYw3s2U4bg3kFFx/ZI0WvQDvCYN7i49cdZx9Xe3bBKnCPYLw2wKwrwH34gLqtvHKex1z+EkcSnd1Zu9FQYf64JFn+ZzUh4WRqXfr+VkJH6qbY3hCIwZAct7M/DyIZunlXG/j4hNZOjMGPpCj6Q9DTPD7sya0zAnjrYZiGOkPQvmkOhYpCrMBo6+gd3S+gn++g9h51g2oGtQ/SEk2L++zxJUpdmyUKym/wV21QcIEk+ePyRu1J89ajaEjChXaQ+3JP3xqyjQrbqKDy7IL9HEgpWGgKXH+UgkWOlhMp2MivcDmSqbnRprpcrLWpcCf8KC9/Jejg/aDDd4P223eCfhF8pQu408Zos6x47N0WBPcAeGEFf6KY/IZTT4g9qhO/5sBRb7FXSSQCEYqxkGIiRlnNMm3iRihGYpzV/CQRbYzFSEgRZIIEkkgxEvhgLEIRoJIbO0VsWaMFdXxQR8iXg489c4lMBPFozAUPamOTZGz20euN/g7Fa1klqKKJkHQ2eqlf341aJX2dLjU9Xtmy4HEk+E5pz+OJ4LmtPI8jKSd1+eSU/dzFgIoMvycQMDgbEEkbNYBRJpIR0YiQExG1gOHZgKGQRDhmiRliflFzhWwBo7MBIyovJAgEDEVA4NjTcQs4OhtwRMVJETUcBrSqRTJpAcdnAyJ3simyzbCmoQM4ORtw0mTTz5Dyo5IzktMbxFO3YnzIs84x6Pf634knamcuOaxp3N4kHgymfIRs1IhkYPlvFE/PFQaG8Cbx1L2mLBsOMUvM8Y3iOXSaAF+ljoDB28TT0V8mkkmT7ajhMEMbpm9B+o+gZidqVBZQSEgF1XyhZEJqRWOiybjmj6AxekJftpIulM3EjwgxpDkLCWdUm3UyqqeNcGiQCQfXQYODJ8aEEzT6D0llknDw9tqoJjReiCPxJOFQO7IsE7y0+Rq9OEkeVFmBOOM3E+90Nnv5Cw==</t>
+          <t xml:space="preserve">CC1:tVfbbttGEP2V7aCP63h5kZDypbBipIEQFUYUwEBJPqzJtbQQtesuVxZUw/9ezJAWL0pi1WhehDU5czhz5swh/QT+8KAggcLZur4onFKbi1o+KuDgbO2Vg+QJriCBv9RGsWt1X1mnbWbmdm3YTO6KwmZmuZZ7wxbFra4qLbd1Zr4cpGG3SpXtcaGVqzNzrYw5vPwxt4p9toVeGQscZpDAtd2t2EwZo7zPzEJvFJs5tdL+H+Uyc1VJw5aFxXvX1rArUzq1rzPz0UmzYcvNrqoOmZntyl6dH9ZO1+xGVlvlNHD4gI+Rj4rd2H1ThaytYUtZKWdsZv6UXrGlV4/K1JmZOeXZVycPlXWZme9qrw1bHChx5mSJeTIzN9KzmdsVm600wOEaEvhYKV+sleuw5ur+vsllc/euZbDtPzNzvWUzZ/cmM38o61aKfZJrk5n51SIzX2xdH6l65oCIvoYkhWWlHy1bFk5u7yoc2vRyejntX7hda6/YV6W6izmHB6fuEeAJJCTQjQg43EECY9b2kATimX8nus/Zq8Hzq8U4pqeKMxBPo/uyeT16PJlxRlMgldqb90nU8N7dS6uo+Vc56Av21eAfdXeK/EpzJwkDab06ux8QchJ83I//v+jhKh3Dcw5I7K3Sq7WHRHDwe7uQBi3MyC3a3Ne9vViQjRwXZOXs7gF3IU2HJgccBuYAOU9hbHXoXD3DgTznaTqseLhMCDIa6Un/DcjQHwcegyBDe8RiXyykX0Srx8GYMXs0ym5YTe5IoT1Lahs42i8ldy7Z5g/XbrDO9PTu7YGFXy3atM7i8fJwyvTczrkxoOegkOf5Mwe/U3UpD72Jf5JmZR+VY19UObRBDqWqC0jgRhcb5pXc1kwb5teK3UnHFtaU8sAMiukX9lnJUpsV21qjDmyvjcG6gov37IGy10o7wmDe4u2XK84+rA/sgtXKPSjjtVHMulK5d+9Qt7WXzkMC4rckEujsztqtVjXWj0eS5akqe+x9R5Pd7DFgIMf+aJpZ9GU2kOY3Zdab0akUBrrB24Pl+OYuDEd6snCjV8FQaz8UMk9h9GI+XTQEGJvJUFYYcVys001o3hbD9UIh1spo6+gdPSb4u3zxMVuDZvm4m0GdvK2kXx8fkJtzWKHwtVmhvPwWf+UW5RcIWgY83sgDbYD1yBMJutROFb460JeH6LLCLiuoPbtgvwZCcBaaEs/vBWeRo+NUcBb7NR5jkZkbberL5UabGq+E78Xl7wQd/Dzo8KdB+91Pgn7msNalutXGaLOqIfFupzh4pfCBtfobpeW3QDMh9qhP/LZTjmaLs0ojHvCQT7jgUx7nDct0ES+EPOaTvOEnjejChMdc8CDnJJBU8JjjjQkPeYC6bs0VsUWDFjT5QZMhno+u9gQCmQiSeAIcgsbmBNmcffB6q/9R5UtblZJlmyEoNnpuXuatWgV9q6403V7bqoQk4rCX2kMy5VDY2kMSCTFt2iffHNbOR1Tk+HWBgMHZgEha3AJGOU9johEhpzzqAMOzAUMuiHCsEivE+qL2EaIDjM4GjKi9kCAQMOQBgeNMJx1gfDZgTM0JHrUcBnRqRDLtACdnAyJ3om2yq7ChoQc4PRtw2lYzrJDqo5ZzktMbxNOMYnKss6kxGM76v4kn6nYuPZ5p3d4kHkymerho1YhkYPtvFM/AFUaG8CbxNLOmKlsOsUqs8Y3iOU6aAF+kjoDB28TT01/O02lbbdxymKMN05ch/X/QsBO1KgsoJaSGGr5QMiGNojXRdNLwR9CYPaXvXEEPFO3Gx4QY0p6FhBM3Zp3GzbYRDi0y4eA5aHEwYkI4Qav/kFQmCAef3hjVlNYLcQRGEg6NI89zDpUtNujFaXovq1rxM35z/pNi8+d/AQ==</t>
         </is>
       </c>
     </row>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -697,29 +697,29 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="7">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="7">
+      <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="7">
+      <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="7">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="7">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -758,12 +758,12 @@
           <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="7">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="7">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -785,19 +785,19 @@
           <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="7">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="7">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="7">
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1051,17 +1051,17 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="7">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr" s="7">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="7">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1122,12 +1122,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr" s="7">
+      <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr" s="7">
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1154,12 +1154,12 @@
           <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr" s="7">
+      <c r="C29" t="inlineStr">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="7">
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1171,7 +1171,7 @@
           <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr" s="7">
+      <c r="B30" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
@@ -1181,7 +1181,7 @@
           <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="7">
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr" s="7">
+      <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
@@ -1233,7 +1233,7 @@
           <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr" s="7">
+      <c r="B34" t="inlineStr">
         <is>
           <t xml:space="preserve">Bud Deflorio</t>
         </is>
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr" s="7">
+      <c r="A35" t="inlineStr">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
@@ -1265,12 +1265,12 @@
           <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr" s="7">
+      <c r="C35" t="inlineStr">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="7">
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">George Hahn</t>
         </is>
@@ -1287,12 +1287,12 @@
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="7">
+      <c r="B36" t="inlineStr">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="7">
+      <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
@@ -1319,7 +1319,7 @@
           <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="7">
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">John Locigno</t>
         </is>
@@ -1353,17 +1353,17 @@
           <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="7">
+      <c r="B39" t="inlineStr">
         <is>
           <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="7">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="7">
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
         </is>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -82,6 +82,13 @@
       <bottom style="medium"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -99,9 +106,10 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +700,7 @@
           <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Shawn McWilliams</t>
         </is>
@@ -714,7 +722,7 @@
           <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Don Andrews</t>
         </is>
@@ -736,7 +744,7 @@
           <t xml:space="preserve">Ross Locigno</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Justin Myers</t>
         </is>
@@ -758,7 +766,7 @@
           <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Dave Powers</t>
         </is>
@@ -780,7 +788,7 @@
           <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">John Baucco</t>
         </is>
@@ -788,6 +796,11 @@
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">JAM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Two guys on the right of the</t>
         </is>
       </c>
     </row>
@@ -802,7 +815,7 @@
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Mike Bregitzer</t>
         </is>
@@ -810,6 +823,11 @@
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">Jim Brown</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">line play the two guys on the</t>
         </is>
       </c>
     </row>
@@ -824,7 +842,7 @@
           <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr" s="9">
         <is>
           <t xml:space="preserve">Doug Bennett</t>
         </is>
@@ -832,6 +850,11 @@
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">Fletcher Stevens</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">left</t>
         </is>
       </c>
     </row>
@@ -1016,6 +1039,11 @@
           <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">Play from senior tees</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
@@ -1142,6 +1170,11 @@
           <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rules: 6 blues, 6 whites, 6</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1164,6 +1197,11 @@
           <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reds; pick as you go (A player</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1186,6 +1224,11 @@
           <t xml:space="preserve">JAM</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">has the final say- but help them</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1206,6 +1249,11 @@
       <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ross Locigno</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">with the strategy!)</t>
         </is>
       </c>
     </row>
@@ -1454,18 +1502,6 @@
       <c r="F48" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">Yellow highlight</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">= Plays the senior tees</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2149,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVfbbttGEP2V7aCP63h5kZDypbBipIEQFUYUwEBJPqzJtbQQtesuVxZUw/9ezJAWL0pi1WhehDU5czhz5swh/QT+8KAggcLZur4onFKbi1o+KuDgbO2Vg+QJriCBv9RGsWt1X1mnbWbmdm3YTO6KwmZmuZZ7wxbFra4qLbd1Zr4cpGG3SpXtcaGVqzNzrYw5vPwxt4p9toVeGQscZpDAtd2t2EwZo7zPzEJvFJs5tdL+H+Uyc1VJw5aFxXvX1rArUzq1rzPz0UmzYcvNrqoOmZntyl6dH9ZO1+xGVlvlNHD4gI+Rj4rd2H1ThaytYUtZKWdsZv6UXrGlV4/K1JmZOeXZVycPlXWZme9qrw1bHChx5mSJeTIzN9KzmdsVm600wOEaEvhYKV+sleuw5ur+vsllc/euZbDtPzNzvWUzZ/cmM38o61aKfZJrk5n51SIzX2xdH6l65oCIvoYkhWWlHy1bFk5u7yoc2vRyejntX7hda6/YV6W6izmHB6fuEeAJJCTQjQg43EECY9b2kATimX8nus/Zq8Hzq8U4pqeKMxBPo/uyeT16PJlxRlMgldqb90nU8N7dS6uo+Vc56Av21eAfdXeK/EpzJwkDab06ux8QchJ83I//v+jhKh3Dcw5I7K3Sq7WHRHDwe7uQBi3MyC3a3Ne9vViQjRwXZOXs7gF3IU2HJgccBuYAOU9hbHXoXD3DgTznaTqseLhMCDIa6Un/DcjQHwcegyBDe8RiXyykX0Srx8GYMXs0ym5YTe5IoT1Lahs42i8ldy7Z5g/XbrDO9PTu7YGFXy3atM7i8fJwyvTczrkxoOegkOf5Mwe/U3UpD72Jf5JmZR+VY19UObRBDqWqC0jgRhcb5pXc1kwb5teK3UnHFtaU8sAMiukX9lnJUpsV21qjDmyvjcG6gov37IGy10o7wmDe4u2XK84+rA/sgtXKPSjjtVHMulK5d+9Qt7WXzkMC4rckEujsztqtVjXWj0eS5akqe+x9R5Pd7DFgIMf+aJpZ9GU2kOY3Zdab0akUBrrB24Pl+OYuDEd6snCjV8FQaz8UMk9h9GI+XTQEGJvJUFYYcVys001o3hbD9UIh1spo6+gdPSb4u3zxMVuDZvm4m0GdvK2kXx8fkJtzWKHwtVmhvPwWf+UW5RcIWgY83sgDbYD1yBMJutROFb460JeH6LLCLiuoPbtgvwZCcBaaEs/vBWeRo+NUcBb7NR5jkZkbberL5UabGq+E78Xl7wQd/Dzo8KdB+91Pgn7msNalutXGaLOqIfFupzh4pfCBtfobpeW3QDMh9qhP/LZTjmaLs0ojHvCQT7jgUx7nDct0ES+EPOaTvOEnjejChMdc8CDnJJBU8JjjjQkPeYC6bs0VsUWDFjT5QZMhno+u9gQCmQiSeAIcgsbmBNmcffB6q/9R5UtblZJlmyEoNnpuXuatWgV9q6403V7bqoQk4rCX2kMy5VDY2kMSCTFt2iffHNbOR1Tk+HWBgMHZgEha3AJGOU9johEhpzzqAMOzAUMuiHCsEivE+qL2EaIDjM4GjKi9kCAQMOQBgeNMJx1gfDZgTM0JHrUcBnRqRDLtACdnAyJ3om2yq7ChoQc4PRtw2lYzrJDqo5ZzktMbxNOMYnKss6kxGM76v4kn6nYuPZ5p3d4kHkymerho1YhkYPtvFM/AFUaG8CbxNLOmKlsOsUqs8Y3iOU6aAF+kjoDB28TT01/O02lbbdxymKMN05ch/X/QsBO1KgsoJaSGGr5QMiGNojXRdNLwR9CYPaXvXEEPFO3Gx4QY0p6FhBM3Zp3GzbYRDi0y4eA5aHEwYkI4Qav/kFQmCAef3hjVlNYLcQRGEg6NI89zDpUtNujFaXovq1rxM35z/pNi8+d/AQ==</t>
+          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2ki/CVn0o4g22i6AugniBAJX0wFgTi7BMuiQdQxvk34sZKdbFuxs3aF4Mhpw5nMuZI+aR+2oLPOZLa5w7W1qA9ZmTD8AFt8Z5sDx+5Bc85n/DGtgl3JfGKpPqK1NoNpO75dKkelHIvWbz5a0qSyU3LtU3ldTsFiBvlnMF1qX6ErSunv+4MsD+NEu10oYLPuMxvzS7FZuB1uB9qudqDWxmYaX8V7CpviilZoulwbNLo9mFzi3sXao/WanXbLHelWWV6tku78T5sbDKsWtZbsAqLvhHvEY+ALs2+zoK6YxmC1mC1SbVf0kPbOHhAbRL9cyCZ1+srEpjU321c15pNq/IcWZljn4y1dfSs5ndLdcbqbnglzzmn0rwywJsi3UF9/e1L7uy75sKNvmn+kpt2MyavU71H2DsCthnWehUX13MU31jnDuU6klwRPSOxwlflOrBsMXSys1diU2LzqPzqLtxWygP7AtAu5kJvrVwjwCPXPKYty3igt/xmA+rtudxGDyJ71h3a/ai8dXFfGjTYcUJiMfWXdq8bD3szNCjDpBC7fT7yKp/dvecKnL+xRp0Cfui8Y+yO0Z+Ibkjhx61XuzdDwpyZHyYj/8/6P4oHcwzwbGwt6BWhedxILjfm7nUKGFablDmvuzN2Zxk5DAgK2t2W5yFJOmLHBe8Jw48EwkfSh0qV0dweJaJJOlH3B8mBBm09Cj/GqSvjz2NQZC+PGKwzxLSDaLhY6/N6D1oZdus2nfA0I4kNQkc5JecW5Vs/Ptj1xtnur39emDgF/PGrZV43O53me5tlRsNOgrKsyx7EtzvwOWy6nT8s9Qr8wCW3UDel0HBc3BLHvNrtVwzD3LjmNLMF8DupGVzo3NZMY1kesf+BJkrvWIbo6Fie6U1xhWefWBb8i5AWcJg3uDx844126JiZ8yB3YL2SgMzNgf7/j3y1nlpPY958Gs8DlDZrTEbBQ7jxyXR8piVnep9h5Nt79GgR8dua+pedGnWo+Y3adbp0TEVerzB495wfHMW+i09GrjBp6DPtR8SWSR88GE+HjQEGIpJn1ZocRis40movxb98UIiOtDKWPpGDwv83XqJYbV6yYphNr04RRNJNz7RK24m+AqJr/QK6eU3+Cs3SL8woGHA5bWsaAKMxzoRoXNlYenLil4eQes1ar1C59kZ+ykMAsFGOsf1h0CwsaVlFAg28QUuJ0Gqr5V254u10g53Rh+C898JOnwT6FSn+mZXgotZxO7KHTjBIrbHVxGtLOTut3qIpWOV2bGVYT9fsG0pK7CskI7qca+0LJmT1Rm723lWQLnF/Q3bK1+QhfNWelhV736hbEZvVii/eyPoJ8ELlcOt0lrpleOxtzsQ3APghQ7+QTb7DScaUMMoT3xOgiU6IT2SsQjFSExFICIxyerG0iZujMRETLO6PsmYNqZiIgIRZoI4mQRiIvBgKkYixFFq9ByxgxotrP3D2iN4OgjpIw+wEmE8mXLBw1pZA1JWs/Vqo75C/pxWCTJvPAKyHT/V74dmQAJ6Hq8UHRemzHk8FnwvledxJPjSOM/jcRBEdfok1f3YxaAUGT5oEDA8GRCLNmkAx5lIJlRGhIzEuAUcnQw4EgEVHKPECDG+cXNF0AKOTwYcU3ojgkDAkQgJHHs6bQEnJwNOKLlAjJsahrSqSRK1gNOTAbF2QZNkG2Fdhg5gdDJg1ETTj5Dio5QzotMryFO3YnqIs44x7Pf6v5Fn3M5ccljTuL2KPOhM8YigYSMWA9N/JXl6qjAQhFeRp+41RdnUEKPEGF9JnkOnCfCZ6ggYvo48Hf5lIomaaCdNDTOUYXqM0r8kdXXGDctCchlRQnW9kDIjakUjosm0rh9Bo3dET+uALgyaiZ8Q4ojmbEQ4k1qsk0k9bYRDg0w4uA4bHLSYEk7Y8H9ELAsIB2+vhSqi8UKcAC0Jh9qRZZngpVmuUYuT5F6WDsQJv5l4I9vs6V8=</t>
         </is>
       </c>
     </row>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -134,144 +134,144 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
+          <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Baucco</t>
+          <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shawn McWilliams</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Fletcher Stevens</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Miers</t>
+          <t xml:space="preserve">JAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Don Andrews</t>
+          <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bud Deflorio</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Palmeri</t>
+          <t xml:space="preserve">Denny Miers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Salerno</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Myers</t>
+          <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pat Bruckman</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">Justin Myers</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
+          <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
     </row>
@@ -283,19 +283,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">Ross Locigno</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ross Locigno</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2ki/CVn0o4g22i6AugniBAJX0wFgTi7BMuiQdQxvk34sZKdbFuxs3aF4Mhpw5nMuZI+aR+2oLPOZLa5w7W1qA9ZmTD8AFt8Z5sDx+5Bc85n/DGtgl3JfGKpPqK1NoNpO75dKkelHIvWbz5a0qSyU3LtU3ldTsFiBvlnMF1qX6ErSunv+4MsD+NEu10oYLPuMxvzS7FZuB1uB9qudqDWxmYaX8V7CpviilZoulwbNLo9mFzi3sXao/WanXbLHelWWV6tku78T5sbDKsWtZbsAqLvhHvEY+ALs2+zoK6YxmC1mC1SbVf0kPbOHhAbRL9cyCZ1+srEpjU321c15pNq/IcWZljn4y1dfSs5ndLdcbqbnglzzmn0rwywJsi3UF9/e1L7uy75sKNvmn+kpt2MyavU71H2DsCthnWehUX13MU31jnDuU6klwRPSOxwlflOrBsMXSys1diU2LzqPzqLtxWygP7AtAu5kJvrVwjwCPXPKYty3igt/xmA+rtudxGDyJ71h3a/ai8dXFfGjTYcUJiMfWXdq8bD3szNCjDpBC7fT7yKp/dvecKnL+xRp0Cfui8Y+yO0Z+Ibkjhx61XuzdDwpyZHyYj/8/6P4oHcwzwbGwt6BWhedxILjfm7nUKGFablDmvuzN2Zxk5DAgK2t2W5yFJOmLHBe8Jw48EwkfSh0qV0dweJaJJOlH3B8mBBm09Cj/GqSvjz2NQZC+PGKwzxLSDaLhY6/N6D1oZdus2nfA0I4kNQkc5JecW5Vs/Ptj1xtnur39emDgF/PGrZV43O53me5tlRsNOgrKsyx7EtzvwOWy6nT8s9Qr8wCW3UDel0HBc3BLHvNrtVwzD3LjmNLMF8DupGVzo3NZMY1kesf+BJkrvWIbo6Fie6U1xhWefWBb8i5AWcJg3uDx844126JiZ8yB3YL2SgMzNgf7/j3y1nlpPY958Gs8DlDZrTEbBQ7jxyXR8piVnep9h5Nt79GgR8dua+pedGnWo+Y3adbp0TEVerzB495wfHMW+i09GrjBp6DPtR8SWSR88GE+HjQEGIpJn1ZocRis40movxb98UIiOtDKWPpGDwv83XqJYbV6yYphNr04RRNJNz7RK24m+AqJr/QK6eU3+Cs3SL8woGHA5bWsaAKMxzoRoXNlYenLil4eQes1ar1C59kZ+ykMAsFGOsf1h0CwsaVlFAg28QUuJ0Gqr5V254u10g53Rh+C898JOnwT6FSn+mZXgotZxO7KHTjBIrbHVxGtLOTut3qIpWOV2bGVYT9fsG0pK7CskI7qca+0LJmT1Rm723lWQLnF/Q3bK1+QhfNWelhV736hbEZvVii/eyPoJ8ELlcOt0lrpleOxtzsQ3APghQ7+QTb7DScaUMMoT3xOgiU6IT2SsQjFSExFICIxyerG0iZujMRETLO6PsmYNqZiIgIRZoI4mQRiIvBgKkYixFFq9ByxgxotrP3D2iN4OgjpIw+wEmE8mXLBw1pZA1JWs/Vqo75C/pxWCTJvPAKyHT/V74dmQAJ6Hq8UHRemzHk8FnwvledxJPjSOM/jcRBEdfok1f3YxaAUGT5oEDA8GRCLNmkAx5lIJlRGhIzEuAUcnQw4EgEVHKPECDG+cXNF0AKOTwYcU3ojgkDAkQgJHHs6bQEnJwNOKLlAjJsahrSqSRK1gNOTAbF2QZNkG2Fdhg5gdDJg1ETTj5Dio5QzotMryFO3YnqIs44x7Pf6v5Fn3M5ccljTuL2KPOhM8YigYSMWA9N/JXl6qjAQhFeRp+41RdnUEKPEGF9JnkOnCfCZ6ggYvo48Hf5lIomaaCdNDTOUYXqM0r8kdXXGDctCchlRQnW9kDIjakUjosm0rh9Bo3dET+uALgyaiZ8Q4ojmbEQ4k1qsk0k9bYRDg0w4uA4bHLSYEk7Y8H9ELAsIB2+vhSqi8UKcAC0Jh9qRZZngpVmuUYuT5F6WDsQJv5l4I9vs6V8=</t>
+          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2ki/CVn0o4g22C2NdBPECASrpgbEmNmGZdEk6hjbIvxczUqyL27WbNi8GTc4czuXMMf3EfbkFHvOFNc5dLCzA+sLJR+CCW+M8WB4/8Sse8z9gDewaHgpjlUn11Kw0m8jdYmFSPV/JvWazxZ0qCiU3LtW3pdTsDiCvlzMF1qX6GrQuX75MDbAvZqGW2nDBJzzm12a3ZBPQGrxP9UytgU0sLJX/BjbVV4XUbL4weHZtNLvSuYW9S/UnK/Wazde7oihTPdnlrTg/rqxy7EYWG7CKC/4Rr5GPwG7MvopCOqPZXBZgtUn179IDm3t4BO1SPbHg2Vcry8LYVE93zivNZiU5TqzM0U+m+kZ6NrG7xXojNRf8msf8UwF+sQLbYE3h4aHyZVP7vq5gnX+qp2rDJtbsdap/A2OXwD7LlU719GqW6lvj3KFUz4Ijonc8Tvi8UI+GzRdWbu4LbFp0GV1G7Y27lfLAvgI0m5ngWwsPCPDEJY950yIu+D2Peb9qex6HwbP4B+t2zU4aT69mfZsWK85APLZu0+a0db8zfY8qQAq11e8jq+7Z/UuqyPmTNWgT9qTx97I7Rj6R3JFDh1one/edghwZH+bj/w+6O0oH80xwLOwdqOXK8zgQ3O/NTGqUMC03KHNf9+ZiRjJyGJClNbstzkKSdEWOC94RB56JhPelDpWrJTg8y0SSdCPuDhOC9Fp6lH8F0tXHjsYgSFceMdgXCWkHUfOx02b07rWyaVbl22NoS5LqBA7yS86NStb+3bHrjDPd3vx6YOBXs9qtkXjc7naZ7m2UGw1aCsqzLHsW3O/A5bJsdfyz1EvzCJbdQt6VQcFzcAse8xu1WDMPcuOY0syvgN1Ly2ZG57JkGsn0jn0BmSu9ZBujoWR7pTXGFV58YFvyXoGyhMG8weOXHWu2q5JdMAd2C9orDczYHOz798hb56X1PObBz/EwQGW3xmwUOIwfl0TL/8wmLDiJWrt8f0uhI3aTb2cIRG9IjtvZnQeR9NW8zQ08PsG1E2PwPSqK7hB0OI+HHbq1RgBvPQxTn2cI2hXNPlGRiA60MpZ+o7sJdOPt5d4pXS+bXu69sETd4nb1+g3nSyS+0kukl9/gp9wg/cKAhgGXN7KkCTAeKUSEzpWFhS9KenkEjdeg8QqdZxfshzAIBBvoHNcfAsGGlpZRINjIr3A5ClJ9o7S7nK+Vdrgz+BBc/krQ4ZtApzrVt7sCXMwidl/swAkWsT2+imhlIXe/VEMsHSvNji0N+/GKbQtZgmUr6ageD0rLgjlZXrD7nWcrKLa4v2F75Vdk4byVHpblu58om8GbFcrv3gj6WfCVyuFOaa300vHY2x0I7gHwQgd/Ipv9hhMNqGGUJz4nwRKdkB7JUIRiIMYiEJEYZVVjaRM3BmIkxllVn2RIG2MxEoEIM0GcTAIxEngwFgMR4ijVeo7YQYUWVv5h5RE8H4T0iQdYiTAejbngYaWsASmr2Xq1Ud8gf0mrAJnXHgHZDp+r90M9IAE9j5eKjlemyHk8FHwvledxJPjCOM/jYRBEVfok1d3YRa8UGT5oEDA8GxCLNqoBh5lIRlRGhIzEsAEcnA04EAEVHKPECDG+YX1F0AAOzwYcUnoDgkDAgQgJHHs6bgBHZwOOKLlADOsahrSqSBI1gOOzAbF2QZ1kE2FVhhZgdDZgVEfTjZDio5QzotMryFO1YnyIs4ox7Pb635Fn2MxccljTuL2KPOhM8YigZiMWA9N/JXk6qtAThFeRp+o1RVnXEKPEGF9JnkOnCfCF6ggYvo48Lf5lIonqaEd1DTOUYXqM0l+SqjrDmmUhuQwooapeSJkBtaIW0WRc1Y+g0Tuip3VAFwb1xI8IcUBzNiCcUSXWyaiaNsKhQSYcXIc1DlqMCSes+T8glgWEg7dXQhXReCFOgJaEQ+3IskzwwizWqMVJ8iALB+KMz0y8kW32/Bc=</t>
         </is>
       </c>
     </row>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
     </row>
@@ -378,7 +378,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="7">
@@ -1233,7 +1233,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denny Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="E7">
@@ -2149,7 +2149,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2ki/CVn0o4g22C2NdBPECASrpgbEmNmGZdEk6hjbIvxczUqyL27WbNi8GTc4czuXMMf3EfbkFHvOFNc5dLCzA+sLJR+CCW+M8WB4/8Sse8z9gDewaHgpjlUn11Kw0m8jdYmFSPV/JvWazxZ0qCiU3LtW3pdTsDiCvlzMF1qX6GrQuX75MDbAvZqGW2nDBJzzm12a3ZBPQGrxP9UytgU0sLJX/BjbVV4XUbL4weHZtNLvSuYW9S/UnK/Wazde7oihTPdnlrTg/rqxy7EYWG7CKC/4Rr5GPwG7MvopCOqPZXBZgtUn179IDm3t4BO1SPbHg2Vcry8LYVE93zivNZiU5TqzM0U+m+kZ6NrG7xXojNRf8msf8UwF+sQLbYE3h4aHyZVP7vq5gnX+qp2rDJtbsdap/A2OXwD7LlU719GqW6lvj3KFUz4Ijonc8Tvi8UI+GzRdWbu4LbFp0GV1G7Y27lfLAvgI0m5ngWwsPCPDEJY950yIu+D2Peb9qex6HwbP4B+t2zU4aT69mfZsWK85APLZu0+a0db8zfY8qQAq11e8jq+7Z/UuqyPmTNWgT9qTx97I7Rj6R3JFDh1one/edghwZH+bj/w+6O0oH80xwLOwdqOXK8zgQ3O/NTGqUMC03KHNf9+ZiRjJyGJClNbstzkKSdEWOC94RB56JhPelDpWrJTg8y0SSdCPuDhOC9Fp6lH8F0tXHjsYgSFceMdgXCWkHUfOx02b07rWyaVbl22NoS5LqBA7yS86NStb+3bHrjDPd3vx6YOBXs9qtkXjc7naZ7m2UGw1aCsqzLHsW3O/A5bJsdfyz1EvzCJbdQt6VQcFzcAse8xu1WDMPcuOY0syvgN1Ly2ZG57JkGsn0jn0BmSu9ZBujoWR7pTXGFV58YFvyXoGyhMG8weOXHWu2q5JdMAd2C9orDczYHOz798hb56X1PObBz/EwQGW3xmwUOIwfl0TL/8wmLDiJWrt8f0uhI3aTb2cIRG9IjtvZnQeR9NW8zQ08PsG1E2PwPSqK7hB0OI+HHbq1RgBvPQxTn2cI2hXNPlGRiA60MpZ+o7sJdOPt5d4pXS+bXu69sETd4nb1+g3nSyS+0kukl9/gp9wg/cKAhgGXN7KkCTAeKUSEzpWFhS9KenkEjdeg8QqdZxfshzAIBBvoHNcfAsGGlpZRINjIr3A5ClJ9o7S7nK+Vdrgz+BBc/krQ4ZtApzrVt7sCXMwidl/swAkWsT2+imhlIXe/VEMsHSvNji0N+/GKbQtZgmUr6ageD0rLgjlZXrD7nWcrKLa4v2F75Vdk4byVHpblu58om8GbFcrv3gj6WfCVyuFOaa300vHY2x0I7gHwQgd/Ipv9hhMNqGGUJz4nwRKdkB7JUIRiIMYiEJEYZVVjaRM3BmIkxllVn2RIG2MxEoEIM0GcTAIxEngwFgMR4ijVeo7YQYUWVv5h5RE8H4T0iQdYiTAejbngYaWsASmr2Xq1Ud8gf0mrAJnXHgHZDp+r90M9IAE9j5eKjlemyHk8FHwvledxJPjCOM/jYRBEVfok1d3YRa8UGT5oEDA8GxCLNqoBh5lIRlRGhIzEsAEcnA04EAEVHKPECDG+YX1F0AAOzwYcUnoDgkDAgQgJHHs6bgBHZwOOKLlADOsahrSqSBI1gOOzAbF2QZ1kE2FVhhZgdDZgVEfTjZDio5QzotMryFO1YnyIs4ox7Pb635Fn2MxccljTuL2KPOhM8YigZiMWA9N/JXk6qtAThFeRp+o1RVnXEKPEGF9JnkOnCfCF6ggYvo48Lf5lIonqaEd1DTOUYXqM0l+SqjrDmmUhuQwooapeSJkBtaIW0WRc1Y+g0Tuip3VAFwb1xI8IcUBzNiCcUSXWyaiaNsKhQSYcXIc1DlqMCSes+T8glgWEg7dXQhXReCFOgJaEQ+3IskzwwizWqMVJ8iALB+KMz0y8kW32/Bc=</t>
+          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2kmwLW/WhiDfYLoy6COIFAlTSA2NNLMIy6ZJ0DG+Qfy9mpFiXbDdu2rwYNDlzOJczx/QD94ct8IQvrXHubGkB1mdO3gMX3BrnwfLkgV/whP8Ja2CXcFcZq0ymZ6bUbCp3y6XJ9KKUe83myxtVVUpuXKavD1KzG4CiWc4VWJfpS9BauadvMwPsd7NUK2244FOe8EuzW7EpaA3eZ3qu1sCmFlbKfwWb6YtKarZYGjy7NJpd6MLC3mX6k5V6zRbrXVUdMj3dFZ1AP5ZWOXYlqw1YxQX/iNfIe2BXZl9HIZ3RbCErsNpk+g/pgS083IN2mZ5a8OyLlYfK2EzPds4rzeYHcpxaWaCfzPSV9Gxqd8v1Rmou+CVP+KcK/LIE22LN4O6u9mUz+74pYZN/pmdqw6bW7HWmfwNjV8A+y1JnenYxz/S1ce5YqkfBEdE7nqR8Ual7wxZLKze3FXYtPo/P4+7GTak8sC8A7WYu+NbCHQI8cMkT3vaIC37LEz6s2p4nYfAo/sG6W7MXjWcX86FNlxYnQH7DvEucE8yHzRm61DFStJ2WP7Pqn90+ZYu8f7EMXc6+aPy99J4jv5DcM4ceu15s33cK8sz4OCL/f9D9aTqa54JjYW9ArUrPk0BwvzdzqVHGtNyg1H3Zm7M5KclxRlbW7LY4DmnaFzoueE8feC5SPpQ7FK+O5vA8F2naj7g/TwgyaOmz/GuQvkT2ZAZB+gqJwT6pSDeIho+9NqP3oJVts2rfAUM7qtQkcFRgcm6FsvEfzF1voun69icEI7+YN36tzON2v810caveaNBRUZ7n+aPgfgeukIdOyz9LvTL3YNk1FH0pFLwAt+QJv1LLNfMgN44pzXwJ7FZaNje6kAemkU3v2O8gC6VXbGM0HNheaY1xhWcf2Ja8S1CWMJg3ePy0Y822PLAz5sBuQXulgRlbgH3/HonrvLSeJzz4ORkFqO7WmI0Ch/Hjknj5n+mEBSdV65bvmxx6Rm/y7U2BGEzJ83b2B0KkQ0HvkQPPX2DbC4PwPTKK/hj0WI+HPb51hgBvPY7TkGgI2pfNIVORiQ60MpZ+qPsJ9OMd5N6r3SCbQe6DsETT4271hh3nK2S+0ivkl9/gp9wg/8KApgGXV/JAI2A8cogYXSgLS18d6PkRtF5R6xU6z87YD2EQCBbpAtcfAsFGlpZxINjYl7gcB5m+UtqdL9ZKO9yJPgTnvxJ0+CbQmc709a4Cl7CY3VY7cILFbI9PI1pZKNwv9RRLxw5mx1aG/XjBtpU8gGWldFSPO6VlxZw8nLHbnWclVFvc37C98iVZOG+lh9Xh3U+UTfRmhfK7N4J+FLxUBdworZVeOZ54uwPBPQBe6OAvZLPfcKIBNYzyxDclWKIT0iMdiVBEYiICEYtxXjeWNnEjEmMxyev6pCPamIixCESYC+JkGoixwIOJiESIo9QIOmIHNVpY+4e1R/B4VNIHHmAlwmQ84YKHtbQGJK1m69VGfYXiKa0KZNF4BGQ7eqxfEM2ABPRGXik6Lk1V8GQk+F4qz5NY8KVxniejIIjr9Emr+7GLQSlyfNIgYHgyIBZt3ACOcpGOqYwIGYtRCxidDBiJgAqOUWKEGN+ouSJoAUcnA44ovYggEDASIYFjTyct4PhkwDElF4hRU8OQVjVJ4hZwcjIg1i5okmwjrMvQAYxPBoybaPoRUnyUck50egV56lZMjnHWMYb9Xv878ozamUuPaxq3V5EHnSkeETRsxGJg+q8kT08VBoLwKvLUvaYomxpilBjjK8lz7DQBPlEdAcPXkafDv1ykcRPtuKlhjjJMr1H6U1JXZ9SwLCSXiBKq64WUiagVjYimk7p+BI3eMb2tA7owaCZ+TIgRzVlEOONarNNxPW2EQ4NMOLgOGxy0mBBO2PA/IpYFhIO310IV03ghToCWhEPtyPNc8Mos16jFaXonKwfihM9cvJFt/vg3</t>
         </is>
       </c>
     </row>

--- a/assets/locigno-outing.xlsx
+++ b/assets/locigno-outing.xlsx
@@ -714,88 +714,88 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Don Andrews</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Fletcher Stevens</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ross Locigno</t>
+          <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Justin Myers</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">Jim Brown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
+          <t xml:space="preserve">Ross Locigno</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Justin Myers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Miers</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">John Baucco</t>
+          <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="1">
@@ -807,22 +807,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pat Bruckman</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jim Brown</t>
+          <t xml:space="preserve">JAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="1">
@@ -834,22 +834,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Miers</t>
+          <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Palmeri</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="9">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="1">
@@ -879,22 +879,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">Bret Traylor</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">Chris Palmeri</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nate Stevens</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jim Brown</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -955,88 +955,88 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Miers</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">Bud Deflorio</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Justin Myers</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">Ryan Weed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alan Scott</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">Bret Traylor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chris Palmeri</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Ryan Miers</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">Frank Skully</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jim Brown</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="7">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dennis Miers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">Bud Deflorio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justin Myers</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fletcher Stevens</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="7">
+      <c r="C20" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ross Locigno</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ryan Miers</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">Frank Skully</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">Dave Powers</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="8">
@@ -1076,22 +1076,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pat Bruckman</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">Fletcher Stevens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1130,44 +1130,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
+          <t xml:space="preserve">Shawn McWilliams</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Chris Palmeri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fletcher Stevens</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bud Deflorio</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Salerno</t>
+          <t xml:space="preserve">Pat Bruckman</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1179,22 +1179,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shawn McWilliams</t>
+          <t xml:space="preserve">Ryan Miers</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Palmeri</t>
+          <t xml:space="preserve">Don Andrews</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">JAM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1206,22 +1206,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Miers</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Don Andrews</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">Ross Locigno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1233,22 +1233,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Miers</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ross Locigno</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1278,22 +1278,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryan Weed</t>
+          <t xml:space="preserve">Zeke Deflorio</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bud Deflorio</t>
+          <t xml:space="preserve">Frank Skully</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brad Sala</t>
+          <t xml:space="preserve">Bret Traylor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jim Brown</t>
+          <t xml:space="preserve">JAM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Locigno</t>
+          <t xml:space="preserve">John Baucco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Scott</t>
+          <t xml:space="preserve">Mike Bregitzer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Powers</t>
+          <t xml:space="preserve">Nate Stevens</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Hahn</t>
+          <t xml:space="preserve">Jeff Myers Jr.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1354,22 +1354,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Miers</t>
+          <t xml:space="preserve">Ryan Weed</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doug Bennett</t>
+          <t xml:space="preserve">Bud Deflorio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Salerno</t>
+          <t xml:space="preserve">Brad Sala</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Locigno</t>
+          <t xml:space="preserve">Jim Brown</t>
         </is>
       </c>
     </row>
@@ -1398,44 +1398,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zeke Deflorio</t>
+          <t xml:space="preserve">Dennis Miers</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Skully</t>
+          <t xml:space="preserve">Doug Bennett</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bret Traylor</t>
+          <t xml:space="preserve">Jason Salerno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAM</t>
+          <t xml:space="preserve">John Locigno</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Baucco</t>
+          <t xml:space="preserve">Joe Locigno</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Bregitzer</t>
+          <t xml:space="preserve">Alan Scott</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nate Stevens</t>
+          <t xml:space="preserve">Dave Powers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeff Myers Jr.</t>
+          <t xml:space="preserve">George Hahn</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC1:tVfbbuM2EP0VLtGHFmA2kmwLW/WhiDfYLoy6COIFAlTSA2NNLMIy6ZJ0DG+Qfy9mpFiXbDdu2rwYNDlzOJczx/QD94ct8IQvrXHubGkB1mdO3gMX3BrnwfLkgV/whP8Ja2CXcFcZq0ymZ6bUbCp3y6XJ9KKUe83myxtVVUpuXKavD1KzG4CiWc4VWJfpS9BauadvMwPsd7NUK2244FOe8EuzW7EpaA3eZ3qu1sCmFlbKfwWb6YtKarZYGjy7NJpd6MLC3mX6k5V6zRbrXVUdMj3dFZ1AP5ZWOXYlqw1YxQX/iNfIe2BXZl9HIZ3RbCErsNpk+g/pgS083IN2mZ5a8OyLlYfK2EzPds4rzeYHcpxaWaCfzPSV9Gxqd8v1Rmou+CVP+KcK/LIE22LN4O6u9mUz+74pYZN/pmdqw6bW7HWmfwNjV8A+y1JnenYxz/S1ce5YqkfBEdE7nqR8Ual7wxZLKze3FXYtPo/P4+7GTak8sC8A7WYu+NbCHQI8cMkT3vaIC37LEz6s2p4nYfAo/sG6W7MXjWcX86FNlxYnQH7DvEucE8yHzRm61DFStJ2WP7Pqn90+ZYu8f7EMXc6+aPy99J4jv5DcM4ceu15s33cK8sz4OCL/f9D9aTqa54JjYW9ArUrPk0BwvzdzqVHGtNyg1H3Zm7M5KclxRlbW7LY4DmnaFzoueE8feC5SPpQ7FK+O5vA8F2naj7g/TwgyaOmz/GuQvkT2ZAZB+gqJwT6pSDeIho+9NqP3oJVts2rfAUM7qtQkcFRgcm6FsvEfzF1voun69icEI7+YN36tzON2v810caveaNBRUZ7n+aPgfgeukIdOyz9LvTL3YNk1FH0pFLwAt+QJv1LLNfMgN44pzXwJ7FZaNje6kAemkU3v2O8gC6VXbGM0HNheaY1xhWcf2Ja8S1CWMJg3ePy0Y822PLAz5sBuQXulgRlbgH3/HonrvLSeJzz4ORkFqO7WmI0Ch/Hjknj5n+mEBSdV65bvmxx6Rm/y7U2BGEzJ83b2B0KkQ0HvkQPPX2DbC4PwPTKK/hj0WI+HPb51hgBvPY7TkGgI2pfNIVORiQ60MpZ+qPsJ9OMd5N6r3SCbQe6DsETT4271hh3nK2S+0ivkl9/gp9wg/8KApgGXV/JAI2A8cogYXSgLS18d6PkRtF5R6xU6z87YD2EQCBbpAtcfAsFGlpZxINjYl7gcB5m+UtqdL9ZKO9yJPgTnvxJ0+CbQmc709a4Cl7CY3VY7cILFbI9PI1pZKNwv9RRLxw5mx1aG/XjBtpU8gGWldFSPO6VlxZw8nLHbnWclVFvc37C98iVZOG+lh9Xh3U+UTfRmhfK7N4J+FLxUBdworZVeOZ54uwPBPQBe6OAvZLPfcKIBNYzyxDclWKIT0iMdiVBEYiICEYtxXjeWNnEjEmMxyev6pCPamIixCESYC+JkGoixwIOJiESIo9QIOmIHNVpY+4e1R/B4VNIHHmAlwmQ84YKHtbQGJK1m69VGfYXiKa0KZNF4BGQ7eqxfEM2ABPRGXik6Lk1V8GQk+F4qz5NY8KVxniejIIjr9Emr+7GLQSlyfNIgYHgyIBZt3ACOcpGOqYwIGYtRCxidDBiJgAqOUWKEGN+ouSJoAUcnA44ovYggEDASIYFjTyct4PhkwDElF4hRU8OQVjVJ4hZwcjIg1i5okmwjrMvQAYxPBoybaPoRUnyUck50egV56lZMjnHWMYb9Xv878ozamUuPaxq3V5EHnSkeETRsxGJg+q8kT08VBoLwKvLUvaYomxpilBjjK8lz7DQBPlEdAcPXkafDv1ykcRPtuKlhjjJMr1H6U1JXZ9SwLCSXiBKq64WUiagVjYimk7p+BI3eMb2tA7owaCZ+TIgRzVlEOONarNNxPW2EQ4NMOLgOGxy0mBBO2PA/IpYFhIO310IV03ghToCWhEPtyPNc8Mos16jFaXonKwfihM9cvJFt/vg3</t>
+          <t xml:space="preserve">CC1:tVZtT+NGEP4re1Y/tJIDdkgimn6o4ND1hC4VIkhITfiwsYd4FWc3Xa+Jcoj/3mfWIbEdSk5qEVIY78488/bM2M+B26woGAaJNUXRSSzRolPIJwrCACeObDB8Di6g8BctSFzRY26sMlN9bTItLmWZJHgYZ3KtxSi5V3mu5LKY6tuN1OKeKN2KI0UWx1ektSpen64NiW8mUXNt4O4STq5MOReXUCLnpnqk4PLS0ly572Sn+iIH0jgxfHdltLjQqaU1gL5YqRdivCjzfDPVl2VaC/RzZuHxRuZLsgpuPrMbJChuzLqKQhbAGsucrIb+n9KRGDt6Io1LeHfizsoN0KBaFk4hmY03vLQyZTs51TfSIdAyWSylho8r+PiSk0sysnusa3p8rGzFtT3ZlnCbP57UEhBmraf6DzJ2TuKrzPBwfTFCDdGcXalewoARXREMJ8E4V08GRbFyOcu5a4NT/NUP7jOFjO6I9ocPYbCy9MgAz4FEsPsewWCGg3bV1sEwjl7Cf9Gu1+yoMhJq69Rp8QOQb6jXifMD6u3mtE2qGH20tZYfaDXvZq/ZMu+PlqHO2aPK76V3iHwkuQODBruOtu+dghwo70bk/w+6OU07dVCbC3tPap65YBiFgVubEaYSa0zLJa+6u7XpjPwm2c3I3JpyxeMwmTQXHe4a+wGjg5lrrTteXrWdEzxAadKMuDlPDNJq6UH+FUhzRTbWDIM0NyQH+7pF6kFs+dhoM1u3WrlvVmXbYmhtK20T2G1gb7xflFv71tw1Jtq7379COHKMXGW3X/N83Gyzd7zf3qxQ26IAeMB2dCUVqdzUWv5V6rl5QnVvKW2uwjBIqUigcqOShXCEdgrUxGUkZtKKkdFAEprZ9El8I5kqPRdLo2kj1grNQ1xx51ysvHVGynoM4Qxfv55Ys8o2oiMKsissbqVJGJuSPTlh4hZOWlA1iH4dnkW83a0xS0UFx8+i5+V/phMX3G+1evne5NABvb1tYwrC1pQctrM5ELhuLfQGOfj+CNuODMJ7ZAybY9BgPV82+FYbAva6G6c20Ri0uTbbTGUmFqSVsf5F3UygGW8r90btWtm0cm+FFW57XK9eu+PBnJkPGjO/3JJ/5ZL5F0d+Gli8Aed5BIxjDnlGp8pS4hAff35Ee6vu3iouHEj+UxxFoejqlOVziGfWiwOIPZex2IvwyaR0cTpe4JdPuufR6e8eOv4Q6Cm+pG7LnIqhGIhZjgURQljzp5GXLKXFb9UUy0JsTCnmRvx8IVa5REdFhkOux6PSMheF3HTErHQio3zF50sMO9yzRuEsiD7ffPrFZ9P9sEK58oOggZ2plO6x3UAScNfZkuCPiB0W9DezGbzxNPAN83nyNyVZTyemxyQK47AbnoW9sB8OHqrGHh523zhkTrYOEdN2oTN2VKHFlX1cWUQvu036HERciXjY6yO2uFqtkV+tZuXUUn3HIhg+yrxAXjl2ejDUGL3qy8EPBj9yjfl14L8KonDA4WDsYwQVhz1IXfzvh31IZz7ULqQeAkbokHDDMqRByNYD/3KLIPf9KafX84jdkDW6HqcHuedxGLPvcdjjwOOwHG9xWKPvcRgp9jhnjORx2PuZxxkwpsfxJfU4Xcg9vCuRvUkWXIzJpCrHD/wC4WN0H17+AQ==</t>
         </is>
       </c>
     </row>
